--- a/data/cammy/inputs/cammy_corner_throw_plus17.xlsx
+++ b/data/cammy/inputs/cammy_corner_throw_plus17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\cammy\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38D993F-A8C2-4C5F-9EE1-C123C549769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAF4E06-BD2A-4939-921B-59582C78945F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="4110" windowWidth="24615" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="3450" yWindow="2160" windowWidth="28365" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>title</t>
   </si>
@@ -60,9 +60,6 @@
     <t>key</t>
   </si>
   <si>
-    <t>cr.HP</t>
-  </si>
-  <si>
     <t>shimmy</t>
   </si>
   <si>
@@ -90,15 +87,9 @@
     <t>reversal DP</t>
   </si>
   <si>
-    <t>cr.LK</t>
-  </si>
-  <si>
     <t>parry</t>
   </si>
   <si>
-    <t>delayed cr.HP</t>
-  </si>
-  <si>
     <t>Cammy1</t>
   </si>
   <si>
@@ -115,6 +106,12 @@
   </si>
   <si>
     <t>Cammy Corner Throw Loop (+17)</t>
+  </si>
+  <si>
+    <t>mw s.MP</t>
+  </si>
+  <si>
+    <t>instant DK</t>
   </si>
 </sst>
 </file>
@@ -176,13 +173,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
@@ -542,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -550,7 +544,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -558,7 +552,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -566,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -576,7 +570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B9BB04-D3D2-4E07-A007-5B16E4AB0AD8}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -598,136 +592,132 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
-        <v>18</v>
-      </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1200</v>
       </c>
       <c r="C2">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="D2">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="E2">
-        <v>3040</v>
+        <v>1200</v>
       </c>
       <c r="F2">
-        <v>3040</v>
-      </c>
-      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-1345</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3040</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>2900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
+      <c r="A3" t="s">
+        <v>23</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1440</v>
+        <v>2000</v>
       </c>
       <c r="D3">
-        <v>1200</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>2660</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
       <c r="G3">
-        <v>2660</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>1200</v>
       </c>
       <c r="D4">
-        <v>1440</v>
+        <v>1200</v>
       </c>
       <c r="E4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2660</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2660</v>
       </c>
       <c r="H4">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -735,15 +725,15 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>-1440</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
         <v>0</v>
       </c>
       <c r="E5">
@@ -756,13 +746,13 @@
         <v>3160</v>
       </c>
       <c r="H5">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-1440</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -773,31 +763,31 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-1440</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1200</v>
+      </c>
+      <c r="D6">
+        <v>1200</v>
       </c>
       <c r="E6">
-        <v>-1440</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>3160</v>
+        <v>-1200</v>
       </c>
       <c r="G6">
-        <v>3160</v>
+        <v>2660</v>
       </c>
       <c r="H6">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>-1440</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -805,107 +795,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>1440</v>
+        <v>1200</v>
       </c>
       <c r="D7">
-        <v>1440</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>-1200</v>
-      </c>
-      <c r="G7">
-        <v>-1200</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
       <c r="H7">
-        <v>3160</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>1070</v>
-      </c>
-      <c r="D8">
-        <v>1070</v>
-      </c>
-      <c r="E8">
-        <v>1110</v>
-      </c>
-      <c r="F8">
-        <v>1110</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>-2100</v>
-      </c>
-      <c r="I8">
-        <v>-1345</v>
-      </c>
-      <c r="J8">
-        <v>1110</v>
-      </c>
-      <c r="K8">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>-2210</v>
-      </c>
-      <c r="D9">
-        <v>1200</v>
-      </c>
-      <c r="E9">
-        <v>-1350</v>
-      </c>
-      <c r="F9">
-        <v>-1200</v>
-      </c>
-      <c r="G9">
-        <v>3040</v>
-      </c>
-      <c r="H9">
-        <v>-2100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>-1350</v>
-      </c>
-      <c r="K9">
-        <v>3040</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
